--- a/downloads_generacion/extracted_energia_c_iny_1024.xlsx
+++ b/downloads_generacion/extracted_energia_c_iny_1024.xlsx
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENTE</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Energía MWh</t>
+          <t>Energía kWh</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
